--- a/MainTop/27.04.2026 Макс Озон/города/САНКТ-ПЕТЕРБУРГ_РФЦ.xlsx
+++ b/MainTop/27.04.2026 Макс Озон/города/САНКТ-ПЕТЕРБУРГ_РФЦ.xlsx
@@ -1,205 +1,212 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr autoCompressPictures="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\27.04.2026 Макс Озон\города\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6385634E-7EE3-4915-956B-9B45B69FE8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView tabRatio="600"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Товарный состав" sheetId="1" r:id="rId3"/>
+    <sheet name="Товарный состав" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
   <si>
-    <t xml:space="preserve">артикул</t>
-  </si>
-  <si>
-    <t xml:space="preserve">имя (необязательно)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">количество</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ozon id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">штрихкод</t>
-  </si>
-  <si>
-    <t xml:space="preserve">признак Super</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ликвидность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">зона размещения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">требуется маркировка "честный знак"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">требуется "эВСД"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Черепашки Ниндзя классика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Черепашки Ниндзя классика</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1463874673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дефицитный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сортируемый товар</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Человек Паук и Веном половинки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Человек Паук и Веном половинки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1463877507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Цветы Черный Силуэт Девушки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Цветы Черный Силуэт Девушки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1425250712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Том и Джерри в очках</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Том и Джерри в очках</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1463877271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Сейлор Мун в куртке Sailor Moon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Сейлор Мун в куртке Sailor Moon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1425275426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Был популярным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Одри Хепбёрн поп арт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Одри Хепбёрн поп арт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1425250637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Популярный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Мишка в кепке делает селфи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Мишка в кепке делает селфи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1463874582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Минни Маус фея костюм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Минни Маус фея костюм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1489754799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Был актуальным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Леопардовое сердце поцелуй губ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Леопардовое сердце поцелуй губ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1425250774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Актуальный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка картина Поцелуй Густава Климта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: картина Поцелуй Густава Климта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1425250579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Был дефицитным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Единорог очки сердечки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Единорог очки сердечки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1463877548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Единорог в облаках</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Единорог в облаках</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1463875075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Dolce Gabbana Дольче Габбана лимоны</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды: Dolce Gabbana Дольче Габбана лимоны</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1425250776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка Динозавры</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Термонаклейка для одежды - термотрансфер "Динозавры" для декора одежды и других предметов из текстиля</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OZN1336985573</t>
+    <t>артикул</t>
+  </si>
+  <si>
+    <t>имя (необязательно)</t>
+  </si>
+  <si>
+    <t>количество</t>
+  </si>
+  <si>
+    <t>ozon id</t>
+  </si>
+  <si>
+    <t>штрихкод</t>
+  </si>
+  <si>
+    <t>признак Super</t>
+  </si>
+  <si>
+    <t>ликвидность</t>
+  </si>
+  <si>
+    <t>зона размещения</t>
+  </si>
+  <si>
+    <t>требуется маркировка "честный знак"</t>
+  </si>
+  <si>
+    <t>требуется "эВСД"</t>
+  </si>
+  <si>
+    <t>Термонаклейка Черепашки Ниндзя классика</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Черепашки Ниндзя классика</t>
+  </si>
+  <si>
+    <t>OZN1463874673</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Дефицитный</t>
+  </si>
+  <si>
+    <t>Сортируемый товар</t>
+  </si>
+  <si>
+    <t>Термонаклейка Человек Паук и Веном половинки</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Человек Паук и Веном половинки</t>
+  </si>
+  <si>
+    <t>OZN1463877507</t>
+  </si>
+  <si>
+    <t>Термонаклейка Цветы Черный Силуэт Девушки</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Черный Силуэт Девушки</t>
+  </si>
+  <si>
+    <t>OZN1425250712</t>
+  </si>
+  <si>
+    <t>Термонаклейка Том и Джерри в очках</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Том и Джерри в очках</t>
+  </si>
+  <si>
+    <t>OZN1463877271</t>
+  </si>
+  <si>
+    <t>Термонаклейка Сейлор Мун в куртке Sailor Moon</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сейлор Мун в куртке Sailor Moon</t>
+  </si>
+  <si>
+    <t>OZN1425275426</t>
+  </si>
+  <si>
+    <t>Был популярным</t>
+  </si>
+  <si>
+    <t>Термонаклейка Одри Хепбёрн поп арт</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Одри Хепбёрн поп арт</t>
+  </si>
+  <si>
+    <t>OZN1425250637</t>
+  </si>
+  <si>
+    <t>Популярный</t>
+  </si>
+  <si>
+    <t>Термонаклейка Мишка в кепке делает селфи</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Мишка в кепке делает селфи</t>
+  </si>
+  <si>
+    <t>OZN1463874582</t>
+  </si>
+  <si>
+    <t>Термонаклейка Минни Маус фея костюм</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Минни Маус фея костюм</t>
+  </si>
+  <si>
+    <t>OZN1489754799</t>
+  </si>
+  <si>
+    <t>Был актуальным</t>
+  </si>
+  <si>
+    <t>Термонаклейка Леопардовое сердце поцелуй губ</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Леопардовое сердце поцелуй губ</t>
+  </si>
+  <si>
+    <t>OZN1425250774</t>
+  </si>
+  <si>
+    <t>Актуальный</t>
+  </si>
+  <si>
+    <t>Термонаклейка картина Поцелуй Густава Климта</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: картина Поцелуй Густава Климта</t>
+  </si>
+  <si>
+    <t>OZN1425250579</t>
+  </si>
+  <si>
+    <t>Был дефицитным</t>
+  </si>
+  <si>
+    <t>Термонаклейка Единорог очки сердечки</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Единорог очки сердечки</t>
+  </si>
+  <si>
+    <t>OZN1463877548</t>
+  </si>
+  <si>
+    <t>Термонаклейка Единорог в облаках</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Единорог в облаках</t>
+  </si>
+  <si>
+    <t>OZN1463875075</t>
+  </si>
+  <si>
+    <t>Термонаклейка Dolce Gabbana Дольче Габбана лимоны</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Dolce Gabbana Дольче Габбана лимоны</t>
+  </si>
+  <si>
+    <t>OZN1425250776</t>
+  </si>
+  <si>
+    <t>Термонаклейка Динозавры</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды - термотрансфер "Динозавры" для декора одежды и других предметов из текстиля</t>
+  </si>
+  <si>
+    <t>OZN1336985573</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -213,23 +220,20 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -238,179 +242,356 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right style="thin"/>
-      <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
+        <color rgb="FF808080"/>
       </left>
       <right style="thin">
-        <color rgb="808080"/>
+        <color rgb="FF808080"/>
       </right>
       <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right style="thin">
-        <color rgb="808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right style="thin">
-        <color rgb="808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="808080"/>
+        <color rgb="FF808080"/>
       </top>
       <bottom style="thin">
-        <color rgb="808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="808080"/>
-      </left>
-      <right style="thin"/>
-      <top style="thin">
-        <color rgb="808080"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="808080"/>
+        <color rgb="FF808080"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+  <a:themeElements>
+    <a:clrScheme name="Стандартная">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Стандартная">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Стандартная">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.31640625" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="57.265625" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.8828125" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="14.31640625" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="14.31640625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="14.31640625" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="28.6328125" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="28.6328125" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="37.22265625" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="37.22265625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="57.28515625" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1" collapsed="1"/>
+    <col min="4" max="6" width="14.28515625" customWidth="1" collapsed="1"/>
+    <col min="7" max="8" width="28.5703125" customWidth="1" collapsed="1"/>
+    <col min="9" max="10" width="37.28515625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="49.3" customHeight="1">
+    <row r="1" spans="1:10" ht="49.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,7 +623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -474,7 +655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -506,7 +687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -538,7 +719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -570,7 +751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -602,7 +783,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -634,7 +815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -666,7 +847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -698,7 +879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -730,7 +911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
@@ -762,7 +943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
@@ -794,7 +975,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
@@ -826,7 +1007,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -858,7 +1039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
